--- a/data/geologie_template_full.xlsx
+++ b/data/geologie_template_full.xlsx
@@ -14991,7 +14991,7 @@
     <t>Date generated</t>
   </si>
   <si>
-    <t>2024-07-24 09:00:01.892120</t>
+    <t>2024-07-24 09:03:32.782536</t>
   </si>
   <si>
     <t>version</t>
